--- a/product_selector_out/STM32U3 series - diff.xlsx
+++ b/product_selector_out/STM32U3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -96,7 +91,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1989</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="18">
@@ -3377,22 +3371,18 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3404,29 +3394,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3436,7 +3422,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3444,70 +3430,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3517,7 +3503,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>33||37</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3525,55 +3511,63 @@
           <t>37</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>33, 37</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>33||37 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3585,22 +3579,18 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3612,137 +3602,117 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>33||37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>33, 37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>33||37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3765,7 +3735,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3788,169 +3758,145 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3973,7 +3919,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3996,169 +3942,145 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4181,7 +4103,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4204,169 +4126,145 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4389,7 +4287,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4412,99 +4310,87 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4516,18 +4402,18 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -4539,1945 +4425,28 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr">
-        <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>47||51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E182" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>47||51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>47||51 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E206" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E211" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E233" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E237" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E240" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E241" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E243"/>
+  <autoFilter ref="A18:E168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3 series - diff.xlsx
+++ b/product_selector_out/STM32U3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,11 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -81,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -91,6 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2018</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="18">
@@ -3371,18 +3377,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3394,25 +3404,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3422,7 +3436,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3430,70 +3444,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33||37</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3503,7 +3517,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>33||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3511,63 +3525,55 @@
           <t>37</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>33, 37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>33||37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3579,18 +3585,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3602,117 +3612,137 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>33||37</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>33, 37</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>33||37 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3735,7 +3765,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3758,145 +3788,169 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3919,7 +3973,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3942,145 +3996,169 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4103,7 +4181,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4126,145 +4204,169 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4287,7 +4389,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4310,87 +4412,99 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -4402,18 +4516,18 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -4425,28 +4539,1945 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>STM32U3C5WI</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>STM32U3B5RI</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>STM32U3B5RG</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>47||51</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>47||51 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>STM32U3C5RI</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>STM32U3B5VI</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>STM32U3B5VI</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>STM32U3C5VI</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>STM32U3C5VI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>STM32U3B5WI</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>STM32U3C5JI</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>STM32U3B5QI</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>STM32U3B5VG</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>STM32U3B5VG</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E220" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>111||114</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>111, 114</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>111||114 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E232" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>106||110</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>106, 110</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>106||110 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
           <t>STM32U3B5JG</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr">
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E168"/>
+  <autoFilter ref="A18:E243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3 series - diff.xlsx
+++ b/product_selector_out/STM32U3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1989</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="18">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1759,17 +1759,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -1840,22 +1840,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1867,67 +1863,59 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1939,69 +1927,81 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33||35||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>33||35||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2175,22 +2175,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2202,95 +2198,99 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2383,22 +2383,18 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2410,61 +2406,57 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2474,46 +2466,46 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2523,7 +2515,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2531,55 +2523,63 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2591,22 +2591,18 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2618,29 +2614,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2650,7 +2642,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2658,97 +2650,97 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>79||82</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>79, 82</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>79||82 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2766,16 +2758,16 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2785,7 +2777,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2793,54 +2785,50 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -2852,30 +2840,34 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2885,24 +2877,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2912,259 +2904,251 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>79||82</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>79, 82</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>79||82 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3174,7 +3158,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3182,85 +3166,77 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -3272,22 +3248,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -3299,22 +3275,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
@@ -3326,7 +3302,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3349,7 +3325,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3372,7 +3348,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3399,7 +3375,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3426,7 +3402,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3453,188 +3429,180 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>33||37</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>33, 37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>33||37 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3644,7 +3612,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3652,108 +3620,104 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>33||37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>33||37 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -3765,30 +3729,34 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3806,16 +3774,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3825,7 +3793,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3833,43 +3801,43 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E140" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3879,24 +3847,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>111||114</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3906,62 +3874,58 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>111, 114</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -3973,30 +3937,34 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4014,16 +3982,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4033,7 +4001,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4041,158 +4009,154 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>111, 114</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>111||114 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -4204,34 +4168,30 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4249,16 +4209,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4268,7 +4228,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4276,97 +4236,89 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>106||110</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4389,7 +4341,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4412,61 +4364,53 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4476,7 +4420,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4484,77 +4428,85 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -4566,22 +4518,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -4593,22 +4545,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -4620,7 +4572,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4643,7 +4595,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4666,7 +4618,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4676,7 +4628,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4684,70 +4636,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4757,24 +4709,24 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>47||51</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4784,62 +4736,58 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>47, 51</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>47||51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -4851,30 +4799,34 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4892,16 +4844,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4911,7 +4863,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4919,185 +4871,177 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E182" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>47||51 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -5109,22 +5053,22 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -5136,22 +5080,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>47 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -5163,134 +5107,134 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>47||51</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>47, 51</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>47||51 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E194" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5313,7 +5257,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5336,53 +5280,61 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5392,7 +5344,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5400,204 +5352,208 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E206" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>47 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -5609,875 +5565,28 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5JG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E211" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E215" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr">
-        <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E220" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E221" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E225" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>111||114</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>111, 114</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>111||114 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E233" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>106||110</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>106, 110</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E236" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>106||110 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="E237" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr"/>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E240" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E241" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E243"/>
+  <autoFilter ref="A18:E210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3 series - diff.xlsx
+++ b/product_selector_out/STM32U3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$213</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="18">
@@ -1343,18 +1343,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1||2</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1366,99 +1370,95 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1||2 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -1497,17 +1497,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>26 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -1632,18 +1632,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1655,99 +1659,95 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -1840,18 +1840,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1863,59 +1867,67 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -1927,81 +1939,69 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>33||35||37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -2067,17 +2067,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>33, 37</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -2148,17 +2148,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33||35||37 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2175,18 +2175,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2198,99 +2202,95 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2383,18 +2383,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2406,99 +2410,95 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2591,18 +2591,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2614,99 +2618,95 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -2799,18 +2799,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2822,99 +2826,95 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2926,18 +2926,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2949,25 +2953,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2977,7 +2985,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2985,63 +2993,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3053,18 +3053,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3076,25 +3080,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3104,7 +3112,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3112,63 +3120,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3180,18 +3180,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3203,25 +3207,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3231,7 +3239,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3239,63 +3247,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3307,18 +3307,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3330,25 +3334,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3358,7 +3366,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3366,63 +3374,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3434,18 +3434,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3457,25 +3461,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3485,7 +3493,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3493,63 +3501,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3561,18 +3561,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3584,25 +3588,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3612,7 +3620,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3620,63 +3628,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3688,18 +3688,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3711,25 +3715,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3739,7 +3747,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3747,63 +3755,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3815,17 +3815,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -3842,17 +3842,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -3896,18 +3896,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3919,99 +3923,95 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4023,18 +4023,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4046,25 +4050,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4074,7 +4082,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4082,63 +4090,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E152" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4150,18 +4150,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4173,25 +4177,29 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4201,7 +4209,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4209,63 +4217,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4277,18 +4277,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4300,59 +4304,67 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -4364,18 +4376,18 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -4387,18 +4399,18 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -4410,81 +4422,69 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E166" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -4550,17 +4550,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -4577,18 +4577,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4600,99 +4604,95 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E173" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4704,22 +4704,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -4731,22 +4731,22 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -4758,18 +4758,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4781,99 +4785,95 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4885,18 +4885,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4908,59 +4912,67 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -4972,81 +4984,69 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5058,22 +5058,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5085,22 +5085,22 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>47 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E191" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5112,18 +5112,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5135,99 +5139,95 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>47 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5239,18 +5239,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5262,25 +5266,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5290,7 +5298,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5298,63 +5306,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E200" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5ZG</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5366,18 +5366,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E202" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5389,25 +5393,29 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5417,7 +5425,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5425,63 +5433,55 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E204" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E205" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QG</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -5493,22 +5493,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5520,22 +5520,22 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>47 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E208" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -5547,18 +5547,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -5570,23 +5574,100 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>47 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr">
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E210" s="3" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E210"/>
+  <autoFilter ref="A18:E213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32U3 series - diff.xlsx
+++ b/product_selector_out/STM32U3 series - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$239</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1999</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="18">
@@ -1095,27 +1095,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1140,9 +1136,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1155,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1167,9 +1163,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1177,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>47||51||52</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>47, 51</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1209,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>47, 51, 52</t>
+          <t>47||51||52</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1221,9 +1217,9 @@
           <t>47, 51</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1236,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>47||51||52 (workbook and API agree)</t>
+          <t>47, 51, 52</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1248,9 +1244,9 @@
           <t>47, 51</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1262,22 +1258,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>47||51||52 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>47, 51</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1302,9 +1298,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1317,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1329,9 +1325,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1339,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1||2</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1356,9 +1352,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1371,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>1||2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1383,9 +1379,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1398,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1||2 (workbook and API agree)</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1410,9 +1406,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1424,18 +1420,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1||2 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1447,13 +1447,13 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -1465,54 +1465,46 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1521,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1537,9 +1529,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1543,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1578,22 +1570,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1602,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>26 (workbook and API agree)</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1618,9 +1610,9 @@
           <t>25</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1632,22 +1624,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1659,22 +1651,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>26 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1683,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1699,9 +1691,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1713,18 +1705,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1736,99 +1732,91 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1828,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1850,7 +1838,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -1867,7 +1855,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1877,7 +1865,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -1894,7 +1882,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1904,7 +1892,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -1921,18 +1909,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1944,59 +1936,67 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2008,108 +2008,92 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>33||35||37</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2105,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33, 35, 37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2148,22 +2132,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>33||35||37 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>33, 37</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2175,22 +2159,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2202,22 +2186,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>33||35||37</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2229,22 +2213,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>33, 35, 37</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2256,18 +2240,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>33||35||37 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>33, 37</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2279,30 +2267,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2312,120 +2304,108 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2437,22 +2417,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2464,18 +2444,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2487,30 +2471,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2520,7 +2508,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -2532,12 +2520,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2547,7 +2535,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -2559,12 +2547,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2574,7 +2562,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
@@ -2586,81 +2574,69 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2672,18 +2648,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2695,25 +2675,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2723,7 +2707,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2731,21 +2715,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2755,46 +2739,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2804,7 +2788,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2812,81 +2796,73 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -2903,25 +2879,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2931,24 +2911,24 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2958,224 +2938,228 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3185,7 +3169,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3193,81 +3177,73 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -3279,30 +3255,34 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3320,16 +3300,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3339,7 +3319,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3347,54 +3327,50 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -3406,18 +3382,18 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -3429,7 +3405,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3456,7 +3432,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3483,7 +3459,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3510,7 +3486,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3533,7 +3509,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3556,34 +3532,30 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3601,16 +3573,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3620,7 +3592,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3628,50 +3600,54 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -3683,61 +3659,53 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3B5ZI</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3747,7 +3715,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3755,158 +3723,154 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32U3B5WG</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5ZI</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -3918,22 +3882,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -3945,22 +3909,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -3972,7 +3936,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3995,7 +3959,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32U3C5WI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4018,34 +3982,30 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3C5QI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4063,16 +4023,16 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4082,7 +4042,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4090,50 +4050,54 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32U3B5RI</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -4145,61 +4109,53 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3B5WG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4209,7 +4165,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4217,77 +4173,85 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>STM32U3B5RG</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -4299,22 +4263,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -4326,22 +4290,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -4353,7 +4317,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4376,7 +4340,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>STM32U3C5RI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4399,18 +4363,18 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3C5WI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -4422,172 +4386,172 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>STM32U3B5VI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>STM32U3C5VI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RI</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -4599,22 +4563,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -4626,22 +4590,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>97 (workbook and API agree)</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -4653,7 +4617,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4676,7 +4640,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32U3B5WI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4699,153 +4663,145 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3B5RG</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>10 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>97 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -4857,18 +4813,18 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32U3C5JI</t>
+          <t>STM32U3C5RI</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -4880,99 +4836,87 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5VI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E184" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>10 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E185" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3C5VI</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -4984,130 +4928,142 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32U3B5QI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STM32U3B5VG</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5117,89 +5073,81 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>97 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E193" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>47 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3B5WI</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -5211,145 +5159,153 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32U3B5JI</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E198" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E199" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>97 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32U3B5ZG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -5361,61 +5317,53 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3C5JI</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E203" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5425,7 +5373,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>10 (workbook and API agree)</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5433,241 +5381,891 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E204" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32U3B5QG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-03-03T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5QI</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E210" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5VG</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>47 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32U3B5JG</t>
+          <t>STM32U3B5JI</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>47 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>STM32U3B5JI</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>STM32U3B5ZG</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>10 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-03-03T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>STM32U3B5QG</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>STM32U3B5JG</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E232" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>47 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr">
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
         <is>
           <t>2026-03-03T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>STM32U3B5JG</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E213"/>
+  <autoFilter ref="A18:E239"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>